--- a/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
+++ b/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T10:14:30+00:00</t>
+    <t>2025-05-12T19:48:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
+++ b/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -27,6 +27,12 @@
     <t>https://www.ehealth.fgov.be/standards/fhir/pss/ValueSet/TrichomonasCodes</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>OID:2.16.840.1.113883.2.51.22.2.48.11</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
@@ -60,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:48:59+00:00</t>
+    <t>2025-05-12T19:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,7 +259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -342,15 +348,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>22</v>
@@ -361,22 +367,22 @@
         <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
         <v>26</v>
       </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -384,6 +390,14 @@
       </c>
       <c r="B16" t="s" s="2">
         <v>28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -402,38 +416,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
+++ b/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:50:51+00:00</t>
+    <t>2025-05-12T19:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
+++ b/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:54:00+00:00</t>
+    <t>2025-05-13T10:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
+++ b/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:10+00:00</t>
+    <t>2025-05-14T06:55:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
+++ b/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:09+00:00</t>
+    <t>2025-05-14T07:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
+++ b/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:28:26+00:00</t>
+    <t>2025-05-14T07:30:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
+++ b/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:17+00:00</t>
+    <t>2025-05-14T07:51:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
+++ b/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:51:32+00:00</t>
+    <t>2025-05-14T08:54:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
+++ b/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:54:50+00:00</t>
+    <t>2025-05-14T13:37:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
+++ b/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:37:41+00:00</t>
+    <t>2025-05-14T14:59:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
+++ b/branches/cpg-profiles/ValueSet-TrichomonasCodes.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:59:57+00:00</t>
+    <t>2025-05-14T15:07:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
